--- a/fix-errors/ig/FRHealthProfessionalLMCDAFHIR.xlsx
+++ b/fix-errors/ig/FRHealthProfessionalLMCDAFHIR.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,13 +105,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-health-professional|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-assigned-entity</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-assigned-entity|0.1.0</t>
   </si>
   <si>
     <t>FRLMHealthProfessional</t>
@@ -183,7 +183,7 @@
     <t>assignedEntity.representedOrganization</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0</t>
   </si>
   <si>
     <t>PractitionerRole</t>
@@ -201,7 +201,7 @@
     <t>PractitionerRole.specialty</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitioner-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitioner-document|0.1.0</t>
   </si>
   <si>
     <t>Practitioner</t>
